--- a/HSIP/41000079736/41000079736_AADT.xlsx
+++ b/HSIP/41000079736/41000079736_AADT.xlsx
@@ -35,7 +35,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Year containing the midpoint date of the study period (9/1/2016-8/31/2026 -&gt; 1 Sep 2021 -&gt; 2021).</t>
+          <t xml:space="preserve">Year containing the midpoint date of the study period 09/01/2016-08/31/2026: =YEAR(B4+(B5-B4)/2).</t>
         </r>
       </text>
     </comment>
@@ -47,7 +47,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Crash count from the TEAAS Intersection Analysis Report, 10-yr report, 29 crashes; used only for the crash rate.</t>
+          <t xml:space="preserve">Crash count from the TEAAS 10-yr Intersection Analysis Report for this study period; used only for the crash rate.</t>
         </r>
       </text>
     </comment>
@@ -69,7 +69,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Year containing the midpoint date of the study period (9/1/2016-8/31/2026 -&gt; 1 Sep 2021 -&gt; 2021).</t>
+          <t xml:space="preserve">Year containing the midpoint date of the study period 09/01/2021-08/31/2026: =YEAR(B4+(B5-B4)/2).</t>
         </r>
       </text>
     </comment>
@@ -81,7 +81,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Crash count from the TEAAS Intersection Analysis Report, 5-yr report, 22 crashes; used only for the crash rate.</t>
+          <t xml:space="preserve">Crash count from the TEAAS 5-yr Intersection Analysis Report for this study period; used only for the crash rate.</t>
         </r>
       </text>
     </comment>
@@ -90,12 +90,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
   <si>
     <t xml:space="preserve">Entering AADT for the 10-yr study - Order# 41000079736, NC 180/NC 226 (S Post Rd) at SR 1103, Cleveland County</t>
   </si>
   <si>
-    <t xml:space="preserve">Method: each leg uses its NCDOT station count for the middle year of the study period. A leg with no count for that year gets a straight-line estimate between the nearest earlier and later published counts, rounded the way NCDOT publishes AADT (nearest 100 at 1,000 vpd and over, nearest 10 below) and marked "estimate". Entering AADT = sum of the four leg AADTs / 2. Exposure (MEV) = entering AADT x 365 x years / 1,000,000. Blue cells are inputs; everything else is a formula reading the Stations sheet.</t>
+    <t xml:space="preserve">Method: each leg uses its NCDOT station count for the middle year of the study period. A leg with no count for that year gets a straight-line estimate between the nearest earlier and later published counts, rounded per the NCDOT/AASHTO AADT rounding chart (nearest 10 below 100, 50 for 100-999, 100 for 1,000-9,999, 500 for 10,000-99,999, 1,000 above) and marked "estimate". Entering AADT = sum of the four leg AADTs / 2, rounded to the nearest hundred as TEAAS Chapter 8 directs. Exposure (MEV) = rounded entering AADT x 365 x years / 1,000,000. Blue cells are inputs; everything else is a formula reading the Stations sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Study period start</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Study length (years)</t>
   </si>
   <si>
-    <t xml:space="preserve">Crashes in the study period (10-yr report, 29 crashes)</t>
+    <t xml:space="preserve">Crashes in the study period (TEAAS 10-yr Intersection Analysis Report)</t>
   </si>
   <si>
     <t xml:space="preserve">Leg</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">Straight-line estimate for the middle year, unrounded</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate rounded as NCDOT publishes</t>
+    <t xml:space="preserve">Estimate rounded per the NCDOT/AASHTO AADT rounding chart</t>
   </si>
   <si>
     <t xml:space="preserve">AADT used for the middle year (vpd)</t>
@@ -167,7 +167,10 @@
     <t xml:space="preserve">Entering AADT = sum / 2 (vpd)</t>
   </si>
   <si>
-    <t xml:space="preserve">Exposure, million entering vehicles = AADT x 365 x years / 1,000,000</t>
+    <t xml:space="preserve">Entering AADT rounded to the nearest hundred (TEAAS Chapter 8) (vpd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure, million entering vehicles = rounded AADT x 365 x years / 1,000,000</t>
   </si>
   <si>
     <t xml:space="preserve">Crash rate (crashes per million entering vehicles)</t>
@@ -251,7 +254,7 @@
     <t xml:space="preserve">Entering AADT for the 5-yr study - Order# 41000079736, NC 180/NC 226 (S Post Rd) at SR 1103, Cleveland County</t>
   </si>
   <si>
-    <t xml:space="preserve">Crashes in the study period (5-yr report, 22 crashes)</t>
+    <t xml:space="preserve">Crashes in the study period (TEAAS 5-yr Intersection Analysis Report)</t>
   </si>
   <si>
     <t xml:space="preserve">Used on the collision diagram and in the study: no (check only)</t>
@@ -425,7 +428,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -470,15 +473,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -778,7 +785,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1009,40 +1016,40 @@
       <c r="A18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="11" t="n">
-        <f aca="false">IFERROR(IF(B17&gt;=1000,ROUND(B17,-2),ROUND(B17,-1)),"")</f>
+      <c r="B18" s="14" t="n">
+        <f aca="false">IFERROR(IF(B17&gt;99999,ROUND(B17,-3),IF(B17&gt;=10000,ROUND(B17/500,0)*500,IF(B17&gt;=1000,ROUND(B17,-2),IF(B17&gt;=100,ROUND(B17/50,0)*50,ROUND(B17,-1))))),"")</f>
         <v>11500</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <f aca="false">IFERROR(IF(C17&gt;=1000,ROUND(C17,-2),ROUND(C17,-1)),"")</f>
-        <v>10200</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <f aca="false">IFERROR(IF(D17&gt;=1000,ROUND(D17,-2),ROUND(D17,-1)),"")</f>
+      <c r="C18" s="14" t="n">
+        <f aca="false">IFERROR(IF(C17&gt;99999,ROUND(C17,-3),IF(C17&gt;=10000,ROUND(C17/500,0)*500,IF(C17&gt;=1000,ROUND(C17,-2),IF(C17&gt;=100,ROUND(C17/50,0)*50,ROUND(C17,-1))))),"")</f>
+        <v>10000</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <f aca="false">IFERROR(IF(D17&gt;99999,ROUND(D17,-3),IF(D17&gt;=10000,ROUND(D17/500,0)*500,IF(D17&gt;=1000,ROUND(D17,-2),IF(D17&gt;=100,ROUND(D17/50,0)*50,ROUND(D17,-1))))),"")</f>
         <v>1400</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <f aca="false">IFERROR(IF(E17&gt;=1000,ROUND(E17,-2),ROUND(E17,-1)),"")</f>
+      <c r="E18" s="14" t="n">
+        <f aca="false">IFERROR(IF(E17&gt;99999,ROUND(E17,-3),IF(E17&gt;=10000,ROUND(E17/500,0)*500,IF(E17&gt;=1000,ROUND(E17,-2),IF(E17&gt;=100,ROUND(E17/50,0)*50,ROUND(E17,-1))))),"")</f>
         <v>1100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="14" t="n">
         <f aca="false">IF(B12&lt;&gt;"",B12,B18)</f>
         <v>11000</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="14" t="n">
         <f aca="false">IF(C12&lt;&gt;"",C12,C18)</f>
         <v>10500</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="14" t="n">
         <f aca="false">IF(D12&lt;&gt;"",D12,D18)</f>
         <v>1400</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="14" t="n">
         <f aca="false">IF(E12&lt;&gt;"",E12,E18)</f>
         <v>1200</v>
       </c>
@@ -1051,19 +1058,19 @@
       <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="15" t="str">
+      <c r="B20" s="16" t="str">
         <f aca="false">IF(B12&lt;&gt;"","count",IF(B18&lt;&gt;"","estimate","no data"))</f>
         <v>count</v>
       </c>
-      <c r="C20" s="15" t="str">
+      <c r="C20" s="16" t="str">
         <f aca="false">IF(C12&lt;&gt;"","count",IF(C18&lt;&gt;"","estimate","no data"))</f>
         <v>count</v>
       </c>
-      <c r="D20" s="15" t="str">
+      <c r="D20" s="16" t="str">
         <f aca="false">IF(D12&lt;&gt;"","count",IF(D18&lt;&gt;"","estimate","no data"))</f>
         <v>estimate</v>
       </c>
-      <c r="E20" s="15" t="str">
+      <c r="E20" s="16" t="str">
         <f aca="false">IF(E12&lt;&gt;"","count",IF(E18&lt;&gt;"","estimate","no data"))</f>
         <v>count</v>
       </c>
@@ -1072,19 +1079,19 @@
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="15" t="str">
+      <c r="B21" s="16" t="str">
         <f aca="false">TEXT(B19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(B20="estimate"," (estimate)","")</f>
         <v>11,000 (2021)</v>
       </c>
-      <c r="C21" s="15" t="str">
+      <c r="C21" s="16" t="str">
         <f aca="false">TEXT(C19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(C20="estimate"," (estimate)","")</f>
         <v>10,500 (2021)</v>
       </c>
-      <c r="D21" s="15" t="str">
+      <c r="D21" s="16" t="str">
         <f aca="false">TEXT(D19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(D20="estimate"," (estimate)","")</f>
         <v>1,400 (2021) (estimate)</v>
       </c>
-      <c r="E21" s="15" t="str">
+      <c r="E21" s="16" t="str">
         <f aca="false">TEXT(E19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(E20="estimate"," (estimate)","")</f>
         <v>1,200 (2021)</v>
       </c>
@@ -1093,7 +1100,7 @@
       <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <f aca="false">SUM(B19:E19)</f>
         <v>24100</v>
       </c>
@@ -1112,8 +1119,8 @@
         <v>25</v>
       </c>
       <c r="B25" s="18" t="n">
-        <f aca="false">B24*365*$B$7/1000000</f>
-        <v>43.9825</v>
+        <f aca="false">ROUND(B24,-2)</f>
+        <v>12100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1121,27 +1128,36 @@
         <v>26</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">$B$8/B25</f>
-        <v>0.659353151821747</v>
+        <f aca="false">B25*365*$B$7/1000000</f>
+        <v>44.165</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="20" t="str">
+      <c r="B27" s="20" t="n">
+        <f aca="false">$B$8/B26</f>
+        <v>0.656628552020831</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="21" t="str">
         <f aca="false">IF(COUNTIF(B20:E20,"estimate")=0,"none",LEFT(IF(B20="estimate",B$10&amp;"; ","")&amp;IF(C20="estimate",C$10&amp;"; ","")&amp;IF(D20="estimate",D$10&amp;"; ","")&amp;IF(E20="estimate",E$10&amp;"; ",""),LEN(IF(B20="estimate",B$10&amp;"; ","")&amp;IF(C20="estimate",C$10&amp;"; ","")&amp;IF(D20="estimate",D$10&amp;"; ","")&amp;IF(E20="estimate",E$10&amp;"; ",""))-2))</f>
         <v>SR 1103 NW leg (Pleasant Dr)</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="3" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1173,12 +1189,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1189,241 +1205,241 @@
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="D4" s="23" t="s">
         <v>35</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>39</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>44</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <v>35.25194</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>35.23435</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>35.24692</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <v>35.24582</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <v>-81.50661</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>-81.51519</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>-81.50978</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="23" t="n">
         <v>-81.50905</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="24" t="n">
         <v>2016</v>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="25" t="n">
         <v>12000</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="25" t="n">
         <v>12000</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="24" t="n">
         <v>2017</v>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <v>11000</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <v>11000</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24" t="n">
+      <c r="D12" s="25"/>
+      <c r="E12" s="25" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="24" t="n">
         <v>2018</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>11500</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>11000</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="E13" s="24"/>
+      <c r="E13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="24" t="n">
         <v>2019</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24" t="n">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="24" t="n">
         <v>2020</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24" t="n">
+      <c r="B15" s="25"/>
+      <c r="C15" s="25" t="n">
         <v>10000</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24" t="n">
+      <c r="D15" s="25"/>
+      <c r="E15" s="25" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>2021</v>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="25" t="n">
         <v>11000</v>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="25" t="n">
         <v>10500</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24" t="n">
+      <c r="D16" s="25"/>
+      <c r="E16" s="25" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>2022</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24" t="n">
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25" t="n">
         <v>1300</v>
       </c>
-      <c r="E17" s="24"/>
+      <c r="E17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="24" t="n">
         <v>2023</v>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="25" t="n">
         <v>11500</v>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="25" t="n">
         <v>10500</v>
       </c>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24" t="n">
+      <c r="D18" s="25"/>
+      <c r="E18" s="25" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="24" t="n">
         <v>2024</v>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="25" t="n">
         <v>11000</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="25" t="n">
         <v>10500</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <v>1500</v>
       </c>
-      <c r="E19" s="24"/>
+      <c r="E19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="n">
+      <c r="A20" s="24" t="n">
         <v>2025</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="25" t="n">
         <v>10500</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="25" t="n">
         <v>10000</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24" t="n">
+      <c r="D20" s="25"/>
+      <c r="E20" s="25" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -1446,7 +1462,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1455,7 +1471,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1503,7 +1519,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>22</v>
@@ -1677,40 +1693,40 @@
       <c r="A18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="11" t="n">
-        <f aca="false">IFERROR(IF(B17&gt;=1000,ROUND(B17,-2),ROUND(B17,-1)),"")</f>
+      <c r="B18" s="14" t="n">
+        <f aca="false">IFERROR(IF(B17&gt;99999,ROUND(B17,-3),IF(B17&gt;=10000,ROUND(B17/500,0)*500,IF(B17&gt;=1000,ROUND(B17,-2),IF(B17&gt;=100,ROUND(B17/50,0)*50,ROUND(B17,-1))))),"")</f>
         <v>11000</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <f aca="false">IFERROR(IF(C17&gt;=1000,ROUND(C17,-2),ROUND(C17,-1)),"")</f>
-        <v>10300</v>
-      </c>
-      <c r="D18" s="11" t="str">
-        <f aca="false">IFERROR(IF(D17&gt;=1000,ROUND(D17,-2),ROUND(D17,-1)),"")</f>
+      <c r="C18" s="14" t="n">
+        <f aca="false">IFERROR(IF(C17&gt;99999,ROUND(C17,-3),IF(C17&gt;=10000,ROUND(C17/500,0)*500,IF(C17&gt;=1000,ROUND(C17,-2),IF(C17&gt;=100,ROUND(C17/50,0)*50,ROUND(C17,-1))))),"")</f>
+        <v>10500</v>
+      </c>
+      <c r="D18" s="14" t="str">
+        <f aca="false">IFERROR(IF(D17&gt;99999,ROUND(D17,-3),IF(D17&gt;=10000,ROUND(D17/500,0)*500,IF(D17&gt;=1000,ROUND(D17,-2),IF(D17&gt;=100,ROUND(D17/50,0)*50,ROUND(D17,-1))))),"")</f>
         <v/>
       </c>
-      <c r="E18" s="11" t="n">
-        <f aca="false">IFERROR(IF(E17&gt;=1000,ROUND(E17,-2),ROUND(E17,-1)),"")</f>
+      <c r="E18" s="14" t="n">
+        <f aca="false">IFERROR(IF(E17&gt;99999,ROUND(E17,-3),IF(E17&gt;=10000,ROUND(E17/500,0)*500,IF(E17&gt;=1000,ROUND(E17,-2),IF(E17&gt;=100,ROUND(E17/50,0)*50,ROUND(E17,-1))))),"")</f>
         <v>1200</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="14" t="n">
         <f aca="false">IF(B12&lt;&gt;"",B12,B18)</f>
         <v>11000</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="14" t="n">
         <f aca="false">IF(C12&lt;&gt;"",C12,C18)</f>
         <v>10500</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="14" t="n">
         <f aca="false">IF(D12&lt;&gt;"",D12,D18)</f>
         <v>1500</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="14" t="n">
         <f aca="false">IF(E12&lt;&gt;"",E12,E18)</f>
         <v>1200</v>
       </c>
@@ -1719,19 +1735,19 @@
       <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="15" t="str">
+      <c r="B20" s="16" t="str">
         <f aca="false">IF(B12&lt;&gt;"","count",IF(B18&lt;&gt;"","estimate","no data"))</f>
         <v>count</v>
       </c>
-      <c r="C20" s="15" t="str">
+      <c r="C20" s="16" t="str">
         <f aca="false">IF(C12&lt;&gt;"","count",IF(C18&lt;&gt;"","estimate","no data"))</f>
         <v>count</v>
       </c>
-      <c r="D20" s="15" t="str">
+      <c r="D20" s="16" t="str">
         <f aca="false">IF(D12&lt;&gt;"","count",IF(D18&lt;&gt;"","estimate","no data"))</f>
         <v>count</v>
       </c>
-      <c r="E20" s="15" t="str">
+      <c r="E20" s="16" t="str">
         <f aca="false">IF(E12&lt;&gt;"","count",IF(E18&lt;&gt;"","estimate","no data"))</f>
         <v>estimate</v>
       </c>
@@ -1740,19 +1756,19 @@
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="15" t="str">
+      <c r="B21" s="16" t="str">
         <f aca="false">TEXT(B19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(B20="estimate"," (estimate)","")</f>
         <v>11,000 (2024)</v>
       </c>
-      <c r="C21" s="15" t="str">
+      <c r="C21" s="16" t="str">
         <f aca="false">TEXT(C19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(C20="estimate"," (estimate)","")</f>
         <v>10,500 (2024)</v>
       </c>
-      <c r="D21" s="15" t="str">
+      <c r="D21" s="16" t="str">
         <f aca="false">TEXT(D19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(D20="estimate"," (estimate)","")</f>
         <v>1,500 (2024)</v>
       </c>
-      <c r="E21" s="15" t="str">
+      <c r="E21" s="16" t="str">
         <f aca="false">TEXT(E19,"#,##0")&amp;" ("&amp;$B$6&amp;")"&amp;IF(E20="estimate"," (estimate)","")</f>
         <v>1,200 (2024) (estimate)</v>
       </c>
@@ -1761,7 +1777,7 @@
       <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <f aca="false">SUM(B19:E19)</f>
         <v>24200</v>
       </c>
@@ -1780,8 +1796,8 @@
         <v>25</v>
       </c>
       <c r="B25" s="18" t="n">
-        <f aca="false">B24*365*$B$7/1000000</f>
-        <v>22.0825</v>
+        <f aca="false">ROUND(B24,-2)</f>
+        <v>12100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1789,27 +1805,36 @@
         <v>26</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">$B$8/B25</f>
-        <v>0.99626400996264</v>
+        <f aca="false">B25*365*$B$7/1000000</f>
+        <v>22.0825</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="20" t="str">
+      <c r="B27" s="20" t="n">
+        <f aca="false">$B$8/B26</f>
+        <v>0.99626400996264</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="21" t="str">
         <f aca="false">IF(COUNTIF(B20:E20,"estimate")=0,"none",LEFT(IF(B20="estimate",B$10&amp;"; ","")&amp;IF(C20="estimate",C$10&amp;"; ","")&amp;IF(D20="estimate",D$10&amp;"; ","")&amp;IF(E20="estimate",E$10&amp;"; ",""),LEN(IF(B20="estimate",B$10&amp;"; ","")&amp;IF(C20="estimate",C$10&amp;"; ","")&amp;IF(D20="estimate",D$10&amp;"; ","")&amp;IF(E20="estimate",E$10&amp;"; ",""))-2))</f>
         <v>SR 1103 SE leg (Pleasant Hill Church Rd)</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
-        <v>29</v>
+      <c r="A30" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
